--- a/artfynd/A 68015-2021 artfynd.xlsx
+++ b/artfynd/A 68015-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123868684</v>
       </c>
       <c r="B2" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>123868771</v>
       </c>
       <c r="B3" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 68015-2021 artfynd.xlsx
+++ b/artfynd/A 68015-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123868684</v>
+        <v>123868771</v>
       </c>
       <c r="B2" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -716,20 +716,24 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572565</v>
+        <v>572577</v>
       </c>
       <c r="R2" t="n">
-        <v>6568441</v>
+        <v>6568430</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123868771</v>
+        <v>123868684</v>
       </c>
       <c r="B3" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,24 +840,20 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572577</v>
+        <v>572565</v>
       </c>
       <c r="R3" t="n">
-        <v>6568430</v>
+        <v>6568441</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 68015-2021 artfynd.xlsx
+++ b/artfynd/A 68015-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123868771</v>
+        <v>123868684</v>
       </c>
       <c r="B2" t="n">
         <v>100257</v>
@@ -716,24 +716,20 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572577</v>
+        <v>572565</v>
       </c>
       <c r="R2" t="n">
-        <v>6568430</v>
+        <v>6568441</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123868684</v>
+        <v>123868771</v>
       </c>
       <c r="B3" t="n">
         <v>100257</v>
@@ -840,20 +836,24 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572565</v>
+        <v>572577</v>
       </c>
       <c r="R3" t="n">
-        <v>6568441</v>
+        <v>6568430</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 68015-2021 artfynd.xlsx
+++ b/artfynd/A 68015-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123868684</v>
+        <v>123868771</v>
       </c>
       <c r="B2" t="n">
         <v>100257</v>
@@ -716,20 +716,24 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572565</v>
+        <v>572577</v>
       </c>
       <c r="R2" t="n">
-        <v>6568441</v>
+        <v>6568430</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123868771</v>
+        <v>123868684</v>
       </c>
       <c r="B3" t="n">
         <v>100257</v>
@@ -836,24 +840,20 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572577</v>
+        <v>572565</v>
       </c>
       <c r="R3" t="n">
-        <v>6568430</v>
+        <v>6568441</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 68015-2021 artfynd.xlsx
+++ b/artfynd/A 68015-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123868684</v>
+        <v>123868771</v>
       </c>
       <c r="B2" t="n">
         <v>100279</v>
@@ -716,20 +716,24 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572565</v>
+        <v>572577</v>
       </c>
       <c r="R2" t="n">
-        <v>6568441</v>
+        <v>6568430</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123868771</v>
+        <v>123868684</v>
       </c>
       <c r="B3" t="n">
         <v>100279</v>
@@ -836,24 +840,20 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572577</v>
+        <v>572565</v>
       </c>
       <c r="R3" t="n">
-        <v>6568430</v>
+        <v>6568441</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 68015-2021 artfynd.xlsx
+++ b/artfynd/A 68015-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123868771</v>
+        <v>123868684</v>
       </c>
       <c r="B2" t="n">
         <v>100279</v>
@@ -716,24 +716,20 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572577</v>
+        <v>572565</v>
       </c>
       <c r="R2" t="n">
-        <v>6568430</v>
+        <v>6568441</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123868684</v>
+        <v>123868771</v>
       </c>
       <c r="B3" t="n">
         <v>100279</v>
@@ -840,20 +836,24 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572565</v>
+        <v>572577</v>
       </c>
       <c r="R3" t="n">
-        <v>6568441</v>
+        <v>6568430</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
